--- a/docs/PRAP_Development_Plan_v1.3.xlsx
+++ b/docs/PRAP_Development_Plan_v1.3.xlsx
@@ -145,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -188,9 +188,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -556,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B97"/>
+  <dimension ref="A1:B107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -597,7 +594,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Development plan (Step 1 deliverable) - change against the v1.2 baseline</t>
+          <t>Development plan (Step 1 deliverable) - FINAL</t>
         </is>
       </c>
     </row>
@@ -621,7 +618,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Change against approved baseline v1.2 - issued for approval</t>
+          <t>FINAL - approved baseline. Step 1 closed.</t>
         </is>
       </c>
     </row>
@@ -664,12 +661,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Baseline</t>
+          <t>Approved by</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>v1.2, approved by Dan 2026-08-01</t>
+          <t>Dan, 2026-08-01 - final issue</t>
         </is>
       </c>
     </row>
@@ -705,7 +702,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>v1.2 once approved; v1.2 remains the baseline until then</t>
+          <t>v1.2 (approved 2026-08-01) and all earlier issues</t>
         </is>
       </c>
     </row>
@@ -864,14 +861,14 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>v1.2 was approved by Dan on 2026-08-01 and remains the baseline. This issue, v1.3, carries one further</t>
+          <t>APPROVED FINAL by Dan on 2026-08-01. This is the last issue of the development plan; Step 1 is complete</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>change requested during Step 2 and needs its own approval before it supersedes v1.2.</t>
+          <t>and work proceeds under the programming specification.</t>
         </is>
       </c>
     </row>
@@ -881,28 +878,28 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>R-04: every sheet of the source workbook now carries at least one free-text note column. Four sheets</t>
+          <t>v1.3 carries change R-04: every sheet of the source workbook now holds at least one free-text note</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>had none - Milestone, ProjectPeriod, PeriodWeightStandard and Lists - and each gains note_1. The other</t>
+          <t>column. Four sheets had none - Milestone, ProjectPeriod, PeriodWeightStandard and Lists - and each gains</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>six already had one: Project and Person carry note_1..note_5, Assignment note_1..note_3, RoleFactor</t>
+          <t>note_1. The other six already had one: Project and Person carry note_1..note_5, Assignment</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>role_note, PersonPeriodWeight reason, and Config note.</t>
+          <t>note_1..note_3, RoleFactor role_note, PersonPeriodWeight reason, and Config note.</t>
         </is>
       </c>
     </row>
@@ -926,90 +923,90 @@
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>dummy dataset gives byte-identical figures to v1.2.</t>
-        </is>
-      </c>
+          <t>dummy dataset gives identical figures to v1.2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>The plan in one page</t>
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>WHAT THIS PLAN NOW FIXES</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Output        One HTML file, opened by double-click on Windows, offline, no install. One Excel</t>
+          <t xml:space="preserve">  65 requirements (sheet 03) as the contract for Steps 2-5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">                workbook alongside it holds the data and remains the archive of record.</t>
+          <t xml:space="preserve">  21 validation rules (sheet 04) applied on import and on every on-screen edit</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="inlineStr"/>
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  11 engineering decisions, C-01 to C-11 (sheet 05), all confirmed</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Calculation   load = project period weight x role factor x person weight x month coverage,</t>
+          <t xml:space="preserve">  a source schema of 10 sheets at version 2 (sheet 04)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">                in FTE where 1.00 FTE = 160 hours per month.</t>
+          <t xml:space="preserve">  the five-step build with a review gate at the end of each (sheet 08)</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                Over-allocated above 1.50 FTE in a month; under-allocated below 0.80 FTE for three</t>
-        </is>
-      </c>
+      <c r="A58" s="6" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">                or more consecutive months, reported as a run.</t>
+          <t>Nothing in this document is open. Six review rounds produced 28 questions and 4 change requests; all 32</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Periods       Clinical Trial: five period names derived from milestone dates and month offsets,</t>
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>are answered and applied, and the review log on sheet 12 carries no open item.</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                with Conduct occurring up to twice where an interim DB lock splits it. Weights come</t>
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>The plan in one page</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">                from the trial's clinical phase.</t>
+          <t xml:space="preserve">  Output        One HTML file, opened by double-click on Windows, offline, no install. One Excel</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">                Others: three periods, dates and weights both entered by hand.</t>
+          <t xml:space="preserve">                workbook alongside it holds the data and remains the archive of record.</t>
         </is>
       </c>
     </row>
@@ -1019,267 +1016,329 @@
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Dashboard     Overall (monthly simulation per project and per person, tables and graphs),</t>
+          <t xml:space="preserve">  Calculation   load = project period weight x role factor x person weight x month coverage,</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">                Source data (project), Source data (person). Every field editable, with identifier</t>
+          <t xml:space="preserve">                in FTE where 1.00 FTE = 160 hours per month.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">                edits cascading to referencing rows.</t>
+          <t xml:space="preserve">                Over-allocated above 1.50 FTE in a month; under-allocated below 0.80 FTE for three</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="6" t="inlineStr"/>
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                or more consecutive months, reported as a run.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Build         Five steps, each ending at a review gate. This document closes Step 1.</t>
+      <c r="A70" s="6" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Periods       Clinical Trial: five period names derived from milestone dates and month offsets,</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>What approving this document means</t>
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                with Conduct occurring up to twice where an interim DB lock splits it. Weights come</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>Gate 1 approval on sheet 12 baselines the 63 requirements on sheet 03 as the contract for Steps 2-5,</t>
+          <t xml:space="preserve">                from the trial's clinical phase.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>and confirms the six engineering decisions C-06 to C-11 on sheet 05 that were proposed but never</t>
+          <t xml:space="preserve">                Others: three periods, dates and weights both entered by hand.</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>explicitly answered across the review rounds. Those six are listed there with their rationale; if any</t>
-        </is>
-      </c>
+      <c r="A75" s="6" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Dashboard     Overall (monthly simulation per project and per person, tables and graphs),</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                Source data (project), Source data (person). Every field editable, with identifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                edits cascading to referencing rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Build         Five steps, each ending at a review gate. This document closes Step 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>What approving this document means</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>Gate 1 approval on sheet 12 baselines the 63 requirements on sheet 03 as the contract for Steps 2-5,</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>and confirms the six engineering decisions C-06 to C-11 on sheet 05 that were proposed but never</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>explicitly answered across the review rounds. Those six are listed there with their rationale; if any</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
           <t>is wrong, say so at approval rather than after.</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
         <is>
           <t>How to read this workbook</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="28" customHeight="1">
-      <c r="A79" s="7" t="inlineStr">
+    <row r="89" ht="28" customHeight="1">
+      <c r="A89" s="7" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B79" s="7" t="inlineStr">
+      <c r="B89" s="7" t="inlineStr">
         <is>
           <t>Contents</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="8" t="inlineStr">
-        <is>
-          <t>00_Cover</t>
-        </is>
-      </c>
-      <c r="B80" s="9" t="inlineStr">
-        <is>
-          <t>Document control, what changed, reading guide.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="10" t="inlineStr">
-        <is>
-          <t>01_Version_History</t>
-        </is>
-      </c>
-      <c r="B81" s="11" t="inlineStr">
-        <is>
-          <t>Change log for this plan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="8" t="inlineStr">
-        <is>
-          <t>02_Scope</t>
-        </is>
-      </c>
-      <c r="B82" s="9" t="inlineStr">
-        <is>
-          <t>Background, objectives, in scope / out of scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="10" t="inlineStr">
-        <is>
-          <t>03_Requirements</t>
-        </is>
-      </c>
-      <c r="B83" s="11" t="inlineStr">
-        <is>
-          <t>Numbered requirement register - the contract for Steps 2-5.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="8" t="inlineStr">
-        <is>
-          <t>04_Data_Model</t>
-        </is>
-      </c>
-      <c r="B84" s="9" t="inlineStr">
-        <is>
-          <t>Every sheet and column of the single source workbook, with rules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="10" t="inlineStr">
-        <is>
-          <t>05_Resource_Logic</t>
-        </is>
-      </c>
-      <c r="B85" s="11" t="inlineStr">
-        <is>
-          <t>The calculation that turns assignments and weights into monthly FTE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="8" t="inlineStr">
-        <is>
-          <t>06_Dashboard_Design</t>
-        </is>
-      </c>
-      <c r="B86" s="9" t="inlineStr">
-        <is>
-          <t>The three dashboard tabs: tables, graphs, filters, editing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="10" t="inlineStr">
-        <is>
-          <t>07_Architecture</t>
-        </is>
-      </c>
-      <c r="B87" s="11" t="inlineStr">
-        <is>
-          <t>Single-file HTML + Excel-on-disk design and the file-access decision.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="8" t="inlineStr">
-        <is>
-          <t>08_WBS_Schedule</t>
-        </is>
-      </c>
-      <c r="B88" s="9" t="inlineStr">
-        <is>
-          <t>The five steps broken into tasks, deliverables and review gates.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="10" t="inlineStr">
-        <is>
-          <t>09_Version_Control</t>
-        </is>
-      </c>
-      <c r="B89" s="11" t="inlineStr">
-        <is>
-          <t>How plan, specification and output files are versioned together.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>10_Risks</t>
+          <t>00_Cover</t>
         </is>
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>Risks and assumptions with mitigations.</t>
+          <t>Document control, what changed, reading guide.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>11_Open_Questions</t>
+          <t>01_Version_History</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>All 28 questions and their answers. Nothing open.</t>
+          <t>Change log for this plan.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
         <is>
+          <t>02_Scope</t>
+        </is>
+      </c>
+      <c r="B92" s="9" t="inlineStr">
+        <is>
+          <t>Background, objectives, in scope / out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="10" t="inlineStr">
+        <is>
+          <t>03_Requirements</t>
+        </is>
+      </c>
+      <c r="B93" s="11" t="inlineStr">
+        <is>
+          <t>Numbered requirement register - the contract for Steps 2-5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t>04_Data_Model</t>
+        </is>
+      </c>
+      <c r="B94" s="9" t="inlineStr">
+        <is>
+          <t>Every sheet and column of the single source workbook, with rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="10" t="inlineStr">
+        <is>
+          <t>05_Resource_Logic</t>
+        </is>
+      </c>
+      <c r="B95" s="11" t="inlineStr">
+        <is>
+          <t>The calculation that turns assignments and weights into monthly FTE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr">
+        <is>
+          <t>06_Dashboard_Design</t>
+        </is>
+      </c>
+      <c r="B96" s="9" t="inlineStr">
+        <is>
+          <t>The three dashboard tabs: tables, graphs, filters, editing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t>07_Architecture</t>
+        </is>
+      </c>
+      <c r="B97" s="11" t="inlineStr">
+        <is>
+          <t>Single-file HTML + Excel-on-disk design and the file-access decision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>08_WBS_Schedule</t>
+        </is>
+      </c>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>The five steps broken into tasks, deliverables and review gates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="10" t="inlineStr">
+        <is>
+          <t>09_Version_Control</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>How plan, specification and output files are versioned together.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="8" t="inlineStr">
+        <is>
+          <t>10_Risks</t>
+        </is>
+      </c>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>Risks and assumptions with mitigations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="10" t="inlineStr">
+        <is>
+          <t>11_Open_Questions</t>
+        </is>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t>All 28 questions and their answers. Nothing open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="8" t="inlineStr">
+        <is>
           <t>12_Review_Log</t>
         </is>
       </c>
-      <c r="B92" s="9" t="inlineStr">
+      <c r="B102" s="9" t="inlineStr">
         <is>
           <t>Every change made across the four review rounds, and why. Gate 1 approval block.</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="3" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="12" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="12" t="inlineStr">
         <is>
           <t>Green = new in v0.2, added from your review answers.</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="13" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="13" t="inlineStr">
         <is>
           <t>Orange = changed in v0.2 as a consequence of your review.</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="14" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="14" t="inlineStr">
         <is>
           <t>Yellow = still needs your input.</t>
         </is>
@@ -1865,7 +1924,7 @@
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>R-04: note column on every source sheet. Awaiting approval.</t>
+          <t>R-04: note column on every source sheet. APPROVED FINAL 2026-08-01 by Dan.</t>
         </is>
       </c>
     </row>
@@ -3637,7 +3696,7 @@
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>All three are settled. Nothing on this sheet is open.</t>
+          <t>All four are settled. Nothing on this sheet is open, and the plan is final.</t>
         </is>
       </c>
     </row>
@@ -3659,7 +3718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5083,7 +5142,7 @@
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>Four sheets gain note_1. Source schema version steps 1 -&gt; 2, so the data model on sheet 04 and the specification's parse contract both change and this issue needs its own approval. Template and dummy workbooks regenerated at v1.2 and re-verified: identical calculation results, confirming the note columns are inert.</t>
+          <t>Four sheets gain note_1. Source schema version steps 1 -&gt; 2, so the data model on sheet 04 and the specification's parse contract both change. Template and dummy workbooks regenerated at v1.2 and re-verified: identical calculation results, confirming the note columns are inert.</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
@@ -5092,155 +5151,195 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>Approval</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>Plan v1.3 approved FINAL by Dan, 2026-08-01.</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>Recorded.</t>
+        </is>
+      </c>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>Step 1 is complete. The plan is closed at 65 requirements, 21 validation rules, 11 decisions and a version-2 source schema. Work proceeds under PRAP_Programming_Specification_v0.2.xlsx, whose sheet 10 carries the one decision still outstanding (S2-01) - a specification matter, not a plan matter.</t>
+        </is>
+      </c>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>Disposition summary</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="7" t="inlineStr">
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>Measure</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>Closed in v0.2</t>
         </is>
       </c>
-      <c r="B51" s="8">
-        <f>COUNTIF(F5:F47,"Closed")</f>
+      <c r="B52" s="8">
+        <f>COUNTIF(F5:F48,"Closed")</f>
         <v/>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="10" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>Open - awaiting your answer</t>
         </is>
       </c>
-      <c r="B52" s="10">
-        <f>COUNTIF(F5:F47,"Open")</f>
+      <c r="B53" s="10">
+        <f>COUNTIF(F5:F48,"Open")</f>
         <v/>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="8" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>Total items</t>
         </is>
       </c>
-      <c r="B53" s="8">
-        <f>COUNTA(A5:A47)</f>
+      <c r="B54" s="8">
+        <f>COUNTA(A5:A48)</f>
         <v/>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>Approval - Gate 1</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="28" customHeight="1">
-      <c r="A56" s="7" t="inlineStr">
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>Approver</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>Decision</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="20" t="inlineStr">
-        <is>
-          <t>PRAP Development Plan v1.0</t>
-        </is>
-      </c>
-      <c r="B57" s="20" t="inlineStr">
-        <is>
-          <t>Dan</t>
-        </is>
-      </c>
-      <c r="C57" s="20" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="D57" s="19" t="inlineStr">
-        <is>
-          <t>APPROVED. Finalise plan v1.0 and proceed to Step 2, beginning with generation of the workbook template and a dummy data file for review.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="20" t="inlineStr">
         <is>
+          <t>PRAP Development Plan v1.0</t>
+        </is>
+      </c>
+      <c r="B58" s="20" t="inlineStr">
+        <is>
+          <t>Dan</t>
+        </is>
+      </c>
+      <c r="C58" s="20" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D58" s="19" t="inlineStr">
+        <is>
+          <t>APPROVED. Finalise plan v1.0 and proceed to Step 2, beginning with generation of the workbook template and a dummy data file for review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="20" t="inlineStr">
+        <is>
           <t>PRAP Development Plan v1.2</t>
         </is>
       </c>
-      <c r="B58" s="20" t="inlineStr">
+      <c r="B59" s="20" t="inlineStr">
         <is>
           <t>Dan</t>
         </is>
       </c>
-      <c r="C58" s="20" t="inlineStr">
+      <c r="C59" s="20" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="D58" s="19" t="inlineStr">
+      <c r="D59" s="19" t="inlineStr">
         <is>
           <t>APPROVED. Finalise plan v1.2 and continue Step 2. This issue supersedes v1.0 as the baseline; R-01, R-02 and R-03 are part of it.</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="8" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="20" t="inlineStr">
         <is>
           <t>PRAP Development Plan v1.3</t>
         </is>
       </c>
-      <c r="B59" s="22" t="inlineStr"/>
-      <c r="C59" s="22" t="inlineStr"/>
-      <c r="D59" s="9" t="inlineStr">
-        <is>
-          <t>Pending your signature. Change R-04: a note column on every source sheet; source schema version steps 1 -&gt; 2. No behaviour change.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="16" t="inlineStr">
-        <is>
-          <t>v1.2 is the approved baseline: the 65 requirements on sheet 03 are the contract for Steps 2-5, and decisions C-01 to C-11 on sheet 05 are confirmed. v1.3 is a change against it and needs the third signature above. Step 2 continues meanwhile - R-04 adds columns and changes no behaviour.</t>
+      <c r="B60" s="20" t="inlineStr">
+        <is>
+          <t>Dan</t>
+        </is>
+      </c>
+      <c r="C60" s="20" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D60" s="19" t="inlineStr">
+        <is>
+          <t>APPROVED - FINAL. Change R-04 accepted; this issue supersedes v1.2 and closes the development plan. Step 1 is complete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="16" t="inlineStr">
+        <is>
+          <t>STEP 1 COMPLETE. v1.3 is the final development plan: the 65 requirements on sheet 03 are the contract for Steps 2-5, decisions C-01 to C-11 on sheet 05 are confirmed, and the source schema is version 2. The plan is closed; further change would need a new approval and a version increment, but none is expected. Work now proceeds under the programming specification.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="F5:F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:F48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,Accepted,Rejected,Deferred,Closed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5750,12 +5849,12 @@
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Change against the v1.2 baseline (R-04): a free-text note column added to every source sheet that lacked one - Milestone, ProjectPeriod, PeriodWeightStandard and Lists each gain note_1. Source schema version steps from 1 to 2. No calculation, validation or UI behaviour changes.</t>
+          <t>Change against the v1.2 baseline (R-04): a free-text note column added to every source sheet that lacked one - Milestone, ProjectPeriod, PeriodWeightStandard and Lists each gain note_1. Source schema version steps from 1 to 2. No calculation, validation or UI behaviour changes. Issued FINAL: this is the last planned issue of the development plan.</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>For approval</t>
+          <t>APPROVED 2026-08-01 by Dan - FINAL</t>
         </is>
       </c>
     </row>
@@ -13831,7 +13930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -14300,7 +14399,7 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Approve plan v1.3.</t>
+          <t>Approve plan v1.3 as final.</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -14310,7 +14409,7 @@
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>Pending you</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14421,12 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>G1</t>
+          <t>G1c</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>GATE 1 - development plan approved by Dan, 2026-08-01. Decisions C-06..C-11 confirmed.</t>
+          <t>STEP 1 COMPLETE - plan v1.3 approved FINAL by Dan, 2026-08-01.</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
@@ -14344,27 +14443,27 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Generate the source workbook template and a dummy data file for review.</t>
+          <t>GATE 1 - development plan approved by Dan, 2026-08-01. Decisions C-06..C-11 confirmed.</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>PRAP_SourceData_Template + _Dummy v1.1</t>
+          <t>Approval recorded on 12_Review_Log</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>Complete - issued for review</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>
@@ -14376,22 +14475,22 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Fix the source workbook schema: exact sheet names, column headers, types, value lists.</t>
+          <t>Generate the source workbook template and a dummy data file for review.</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Specification sheet 'Data schema'</t>
+          <t>PRAP_SourceData_Template + _Dummy v1.1</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Complete - issued for review</t>
         </is>
       </c>
     </row>
@@ -14403,22 +14502,22 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Specify the calculation engine as pseudocode plus the worked example as an acceptance test.</t>
+          <t>Fix the source workbook schema: exact sheet names, column headers, types, value lists.</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>Specification sheet 'Calculation'</t>
+          <t>Specification sheet 'Data schema'</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -14430,12 +14529,12 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Specify period derivation per project type, and the over/under-allocation detection.</t>
+          <t>Specify the calculation engine as pseudocode plus the worked example as an acceptance test.</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
@@ -14457,17 +14556,17 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Specify import validation rules V-01..V-21 and the findings report.</t>
+          <t>Specify period derivation per project type, and the over/under-allocation detection.</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Specification sheet 'Validation'</t>
+          <t>Specification sheet 'Calculation'</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
@@ -14484,17 +14583,17 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Specify each dashboard tab: every table, column, graph, filter and interaction.</t>
+          <t>Specify import validation rules V-01..V-21 and the findings report.</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Specification sheet 'UI spec'</t>
+          <t>Specification sheet 'Validation'</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -14511,17 +14610,17 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Specify on-screen editing, the dirty-state model and export round-tripping.</t>
+          <t>Specify each dashboard tab: every table, column, graph, filter and interaction.</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Specification sheet 'Editing &amp; IO'</t>
+          <t>Specification sheet 'UI spec'</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
@@ -14538,17 +14637,17 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Specify the version/compatibility check.</t>
+          <t>Specify on-screen editing, the dirty-state model and export round-tripping.</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Specification sheet 'IO &amp; versioning'</t>
+          <t>Specification sheet 'Editing &amp; IO'</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -14565,17 +14664,17 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Build the requirement-to-specification traceability matrix.</t>
+          <t>Specify the version/compatibility check.</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>Specification sheet 'Traceability'</t>
+          <t>Specification sheet 'IO &amp; versioning'</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
@@ -14592,17 +14691,17 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>G2</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>GATE 2 - programming specification approved.</t>
+          <t>Build the requirement-to-specification traceability matrix.</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>PRAP_Programming_Specification_v1.0.xlsx</t>
+          <t>Specification sheet 'Traceability'</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -14614,22 +14713,22 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>G2</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>High-level UI design: tab structure, page regions, navigation. No code behind it.</t>
+          <t>GATE 2 - programming specification approved.</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Prototype HTML (UI only)</t>
+          <t>PRAP_Programming_Specification_v1.0.xlsx</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
@@ -14646,17 +14745,17 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Requester reviews the high-level component design.</t>
+          <t>High-level UI design: tab structure, page regions, navigation. No code behind it.</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Review comments</t>
+          <t>Prototype HTML (UI only)</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -14673,17 +14772,17 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Final UI design with clear per-component requirements.</t>
+          <t>Requester reviews the high-level component design.</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>Prototype HTML v1.0 + component list</t>
+          <t>Review comments</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
@@ -14700,17 +14799,17 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>GATE 3 - final design and component list approved. Code generation starts only for approved components.</t>
+          <t>Final UI design with clear per-component requirements.</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Approved component list</t>
+          <t>Prototype HTML v1.0 + component list</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -14722,22 +14821,22 @@
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>IO layer: workbook load, sheet/column mapping, export.</t>
+          <t>GATE 3 - final design and component list approved. Code generation starts only for approved components.</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>Application code</t>
+          <t>Approved component list</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
@@ -14754,12 +14853,12 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Validation layer: rules V-01..V-21 and the findings report.</t>
+          <t>IO layer: workbook load, sheet/column mapping, export.</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
@@ -14781,12 +14880,12 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>Model layer, Lists and Config handling.</t>
+          <t>Validation layer: rules V-01..V-21 and the findings report.</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
@@ -14808,12 +14907,12 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Edit buffer: on-screen editing, dirty state, per-edit validation.</t>
+          <t>Model layer, Lists and Config handling.</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
@@ -14835,17 +14934,17 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Calculation engine, verified against the worked example.</t>
+          <t>Edit buffer: on-screen editing, dirty state, per-edit validation.</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>Application code + test evidence</t>
+          <t>Application code</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
@@ -14862,17 +14961,17 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Overall tab: tables, graphs, filters, over/under-allocation flagging.</t>
+          <t>Calculation engine, verified against the worked example.</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Application code</t>
+          <t>Application code + test evidence</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -14889,12 +14988,12 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>Source data (project) and Source data (person) tabs.</t>
+          <t>Overall tab: tables, graphs, filters, over/under-allocation flagging.</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
@@ -14916,17 +15015,17 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Blank source workbook template with value lists and example rows.</t>
+          <t>Source data (project) and Source data (person) tabs.</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>PRAP_SourceData template</t>
+          <t>Application code</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -14943,17 +15042,17 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>Requester reviews output against real data; refinements folded in.</t>
+          <t>Blank source workbook template with value lists and example rows.</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>Updated code</t>
+          <t>PRAP_SourceData template</t>
         </is>
       </c>
       <c r="E44" s="10" t="inlineStr">
@@ -14970,17 +15069,17 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>G4</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>GATE 4 - application functionally complete.</t>
+          <t>Requester reviews output against real data; refinements folded in.</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>PRAP_Application_v0.9.html</t>
+          <t>Updated code</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -14992,22 +15091,22 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>G4</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>Full pass over the traceability matrix: every Must requirement demonstrated.</t>
+          <t>GATE 4 - application functionally complete.</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>Completed traceability matrix</t>
+          <t>PRAP_Application_v0.9.html</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr">
@@ -15024,17 +15123,17 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Test on a clean Windows PC in Edge and Chrome, offline.</t>
+          <t>Full pass over the traceability matrix: every Must requirement demonstrated.</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>Test evidence</t>
+          <t>Completed traceability matrix</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -15051,17 +15150,17 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>Write the user guide: folder layout, how to load, how to maintain source data.</t>
+          <t>Test on a clean Windows PC in Edge and Chrome, offline.</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>User guide</t>
+          <t>Test evidence</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
@@ -15078,17 +15177,17 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Final version alignment across plan, specification and application.</t>
+          <t>Write the user guide: folder layout, how to load, how to maintain source data.</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Version alignment table (sheet 09)</t>
+          <t>User guide</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -15105,90 +15204,117 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>Final version alignment across plan, specification and application.</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>Version alignment table (sheet 09)</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
           <t>G5</t>
         </is>
       </c>
-      <c r="C50" s="11" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
         <is>
           <t>GATE 5 - release.</t>
         </is>
       </c>
-      <c r="D50" s="11" t="inlineStr">
+      <c r="D51" s="9" t="inlineStr">
         <is>
           <t>PRAP_Application_v1.0.html</t>
         </is>
       </c>
-      <c r="E50" s="10" t="inlineStr">
+      <c r="E51" s="8" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>Progress</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="28" customHeight="1">
-      <c r="A53" s="7" t="inlineStr">
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>Measure</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="8" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>Tasks total</t>
         </is>
       </c>
-      <c r="B54" s="8">
-        <f>COUNTA(B5:B50)</f>
+      <c r="B55" s="8">
+        <f>COUNTA(B5:B51)</f>
         <v/>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="10" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
-      <c r="B55" s="10">
-        <f>COUNTIF(E5:E50,"Complete")+COUNTIF(E5:E50,"Complete - issued for review")</f>
+      <c r="B56" s="10">
+        <f>COUNTIF(E5:E51,"Complete")+COUNTIF(E5:E51,"Complete - issued for review")</f>
         <v/>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="8" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
         <is>
           <t>Awaiting the requester</t>
         </is>
       </c>
-      <c r="B56" s="8">
-        <f>COUNTIF(E5:E50,"Pending you")</f>
+      <c r="B57" s="8">
+        <f>COUNTIF(E5:E51,"Pending you")</f>
         <v/>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="10" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="B57" s="10">
-        <f>COUNTIF(E5:E50,"Not started")</f>
+      <c r="B58" s="10">
+        <f>COUNTIF(E5:E51,"Not started")</f>
         <v/>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="16" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="16" t="inlineStr">
         <is>
           <t>No duration estimates: the pace is set by review turnaround at each gate, not by build effort.</t>
         </is>
@@ -15196,7 +15322,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E5:E50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not started,In progress,Pending you,Complete - issued for review,Complete,Blocked"</formula1>
     </dataValidation>
   </dataValidations>
